--- a/july 2026/LMT_JULY_26/July Orders/Jalal Sons Behria Orchard.xlsx
+++ b/july 2026/LMT_JULY_26/July Orders/Jalal Sons Behria Orchard.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9ADC263-7620-4404-9CD6-DCDEE45FB3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DCBF877-1B17-4238-A885-1688DD8D49FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -373,13 +373,13 @@
     <t>Jalal Sons (Bahira Orchard)</t>
   </si>
   <si>
-    <t>Customer Name : Jalal Sons  (Bahria Orchard)</t>
+    <t>1010737-1</t>
   </si>
   <si>
-    <t>Address: Bahria Orchard</t>
+    <t>Customer Name : Jalal Sons  (warehouse)</t>
   </si>
   <si>
-    <t>1010737-1</t>
+    <t>Address: Chatri Chowk</t>
   </si>
 </sst>
 </file>
@@ -3345,7 +3345,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -3373,7 +3373,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -4566,7 +4566,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -4594,7 +4594,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -5787,7 +5787,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -5815,7 +5815,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -7008,7 +7008,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -7036,7 +7036,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -8229,7 +8229,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -8257,7 +8257,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -9450,7 +9450,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -9478,7 +9478,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -10668,7 +10668,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -10696,7 +10696,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -11885,7 +11885,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -11913,7 +11913,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -13102,7 +13102,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -13130,7 +13130,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -14319,7 +14319,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -14347,7 +14347,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -18286,7 +18286,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -18314,7 +18314,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -19503,7 +19503,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -19531,7 +19531,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -20720,7 +20720,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -20748,7 +20748,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -21937,7 +21937,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -21965,7 +21965,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -23160,7 +23160,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -23188,7 +23188,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -23448,11 +23448,11 @@
       </c>
       <c r="T15" s="162" t="str">
         <f>+'2'!A5</f>
-        <v>Customer Name : Jalal Sons  (Bahria Orchard)</v>
+        <v>Customer Name : Jalal Sons  (warehouse)</v>
       </c>
       <c r="U15" s="163">
         <f>+'2'!P35</f>
-        <v>0</v>
+        <v>312032.4366825</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23497,27 +23497,27 @@
       </c>
       <c r="K16" s="170">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
-        <v>0</v>
+        <v>1836.1875000000002</v>
       </c>
       <c r="L16" s="173">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>0</v>
+        <v>7869.375</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>0</v>
+        <v>-9705.5625</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>0</v>
+        <v>7696.2487499999997</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>0</v>
+        <v>252.26593124999999</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>0</v>
+        <v>-1757.0478187500003</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23571,27 +23571,27 @@
       </c>
       <c r="K17" s="170">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
-        <v>0</v>
+        <v>1836.1875000000002</v>
       </c>
       <c r="L17" s="173">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>0</v>
+        <v>7869.375</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>0</v>
+        <v>-9705.5625</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>0</v>
+        <v>7696.2487499999997</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>0</v>
+        <v>252.26593124999999</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-1757.0478187500003</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -23715,27 +23715,27 @@
       </c>
       <c r="K19" s="170">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>101.69600000000001</v>
+        <v>2644.096</v>
       </c>
       <c r="L19" s="173">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>435.84</v>
+        <v>11331.84</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>2368.0639999999999</v>
+        <v>-11070.335999999999</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>426.25151999999997</v>
+        <v>11082.53952</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>13.971577599999998</v>
+        <v>363.2610176</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>2808.2870975999995</v>
+        <v>375.46453760000094</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -23785,27 +23785,27 @@
       </c>
       <c r="K20" s="170">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>101.69600000000001</v>
+        <v>2644.096</v>
       </c>
       <c r="L20" s="173">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>435.84</v>
+        <v>11331.84</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>2368.0639999999999</v>
+        <v>-11070.335999999999</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>426.25151999999997</v>
+        <v>11082.53952</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>13.971577599999998</v>
+        <v>363.2610176</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>2808.2870975999995</v>
+        <v>375.46453760000094</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -23855,27 +23855,27 @@
       </c>
       <c r="K21" s="170">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
-        <v>203.39200000000002</v>
+        <v>2745.7919999999999</v>
       </c>
       <c r="L21" s="173">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>871.68</v>
+        <v>11767.68</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>4736.1279999999997</v>
+        <v>-8702.2720000000008</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>852.50303999999994</v>
+        <v>11508.79104</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>27.943155199999996</v>
+        <v>377.23259519999999</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>5616.5741951999989</v>
+        <v>3183.7516351999993</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24126,27 +24126,27 @@
       </c>
       <c r="K25" s="176">
         <f t="shared" si="3"/>
-        <v>406.78400000000005</v>
+        <v>11706.359</v>
       </c>
       <c r="L25" s="177">
         <f t="shared" si="3"/>
-        <v>1743.36</v>
+        <v>50170.11</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>9472.2559999999994</v>
+        <v>-50254.069000000003</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>1705.0060799999999</v>
+        <v>49066.367580000006</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>55.886310399999992</v>
+        <v>1608.2864929000002</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>11233.148390399998</v>
+        <v>420.58507290000034</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24276,7 +24276,7 @@
       </c>
       <c r="U30" s="164">
         <f>SUM(U14:U28)</f>
-        <v>11233.148390399998</v>
+        <v>323265.58507289999</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24330,7 +24330,7 @@
       <c r="O33" s="239"/>
       <c r="P33" s="152">
         <f>L25</f>
-        <v>1743.36</v>
+        <v>50170.11</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24351,7 +24351,7 @@
       <c r="O34" s="239"/>
       <c r="P34" s="153">
         <f>K25</f>
-        <v>406.78400000000005</v>
+        <v>11706.359</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24373,7 +24373,7 @@
       <c r="O35" s="239"/>
       <c r="P35" s="152">
         <f>P32-P33-P34</f>
-        <v>9472.2559999999994</v>
+        <v>-50254.069000000003</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="P36" s="152">
         <f>N25</f>
-        <v>1705.0060799999999</v>
+        <v>49066.367580000006</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24420,7 +24420,7 @@
       <c r="O37" s="241"/>
       <c r="P37" s="152">
         <f>P35+P36</f>
-        <v>11177.262079999999</v>
+        <v>-1187.7014199999976</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="P38" s="152">
         <f>O38*P37</f>
-        <v>279.43155199999995</v>
+        <v>-29.692535499999941</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24455,7 +24455,7 @@
       <c r="O39" s="219"/>
       <c r="P39" s="159">
         <f>P37+P38</f>
-        <v>11456.693631999999</v>
+        <v>-1217.3939554999974</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24627,7 +24627,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -24655,7 +24655,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -24748,7 +24748,7 @@
         <v>95</v>
       </c>
       <c r="B10" s="75" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -24823,7 +24823,7 @@
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="242"/>
       <c r="B13" s="75" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -25795,12 +25795,12 @@
     <col min="8" max="8" width="5.453125" customWidth="1"/>
     <col min="9" max="9" width="11.54296875" customWidth="1"/>
     <col min="10" max="10" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="10" style="69" customWidth="1"/>
-    <col min="15" max="15" width="9.54296875" customWidth="1"/>
-    <col min="16" max="16" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.81640625" style="69" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
     <col min="17" max="17" width="4.54296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.26953125" bestFit="1" customWidth="1"/>
   </cols>
@@ -25854,7 +25854,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -25869,7 +25869,7 @@
     </row>
     <row r="5" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="245" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B5" s="245"/>
       <c r="C5" s="245"/>
@@ -25882,7 +25882,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -25891,7 +25891,7 @@
     </row>
     <row r="6" spans="1:19 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="200" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B6" s="200"/>
       <c r="C6" s="200"/>
@@ -26175,36 +26175,38 @@
         <f>VLOOKUP(A16,'[1]Cust. Price List'!D6:M14,10,0)</f>
         <v>52.462499999999999</v>
       </c>
-      <c r="G16" s="99"/>
+      <c r="G16" s="99">
+        <v>25</v>
+      </c>
       <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>0</v>
+        <v>52462.5</v>
       </c>
       <c r="J16" s="102"/>
       <c r="K16" s="103">
         <f>I16*3.5%</f>
-        <v>0</v>
+        <v>1836.1875000000002</v>
       </c>
       <c r="L16" s="104">
         <f>I16*15%</f>
-        <v>0</v>
+        <v>7869.375</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>0</v>
+        <v>42756.9375</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>0</v>
+        <v>7696.2487499999997</v>
       </c>
       <c r="O16" s="106">
         <f>(N16+M16)*$O$15</f>
-        <v>0</v>
+        <v>252.26593124999999</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>0</v>
+        <v>50705.452181250002</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -26235,36 +26237,38 @@
         <f>VLOOKUP(A17,'[1]Cust. Price List'!D7:M15,10,0)</f>
         <v>52.462499999999999</v>
       </c>
-      <c r="G17" s="113"/>
+      <c r="G17" s="113">
+        <v>25</v>
+      </c>
       <c r="H17" s="114"/>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>0</v>
+        <v>52462.5</v>
       </c>
       <c r="J17" s="116"/>
       <c r="K17" s="103">
         <f t="shared" ref="K17:K21" si="3">I17*3.5%</f>
-        <v>0</v>
+        <v>1836.1875000000002</v>
       </c>
       <c r="L17" s="104">
         <f t="shared" ref="L17:L21" si="4">I17*15%</f>
-        <v>0</v>
+        <v>7869.375</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>0</v>
+        <v>42756.9375</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7696.2487499999997</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>0</v>
+        <v>252.26593124999999</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50705.452181250002</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -26351,36 +26355,38 @@
         <f>VLOOKUP(A19,'[1]Cust. Price List'!D9:M17,10,0)</f>
         <v>72.64</v>
       </c>
-      <c r="G19" s="113"/>
+      <c r="G19" s="113">
+        <v>25</v>
+      </c>
       <c r="H19" s="114"/>
       <c r="I19" s="115">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>72640</v>
       </c>
       <c r="J19" s="116"/>
       <c r="K19" s="103">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2542.4</v>
       </c>
       <c r="L19" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10896</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>59201.600000000006</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10656.288</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>349.28944000000001</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>70207.177439999999</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26407,36 +26413,38 @@
         <f>VLOOKUP(A20,'[1]Cust. Price List'!D10:M18,10,0)</f>
         <v>72.64</v>
       </c>
-      <c r="G20" s="113"/>
+      <c r="G20" s="113">
+        <v>25</v>
+      </c>
       <c r="H20" s="114"/>
       <c r="I20" s="115">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>72640</v>
       </c>
       <c r="J20" s="116"/>
       <c r="K20" s="103">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2542.4</v>
       </c>
       <c r="L20" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10896</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>59201.600000000006</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10656.288</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>349.28944000000001</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>70207.177439999999</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26463,36 +26471,38 @@
         <f>VLOOKUP(A21,'[1]Cust. Price List'!D11:M19,10,0)</f>
         <v>72.64</v>
       </c>
-      <c r="G21" s="113"/>
+      <c r="G21" s="113">
+        <v>25</v>
+      </c>
       <c r="H21" s="114"/>
       <c r="I21" s="115">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>72640</v>
       </c>
       <c r="J21" s="116"/>
       <c r="K21" s="103">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2542.4</v>
       </c>
       <c r="L21" s="104">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>10896</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>59201.600000000006</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10656.288</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>349.28944000000001</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>70207.177439999999</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26674,7 +26684,7 @@
       <c r="F25" s="251"/>
       <c r="G25" s="134">
         <f t="shared" ref="G25:M25" si="9">SUM(G16:G24)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
@@ -26682,32 +26692,32 @@
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>322845</v>
       </c>
       <c r="J25" s="137"/>
       <c r="K25" s="138">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>11299.575000000001</v>
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>48426.75</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>263118.67500000005</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>0</v>
+        <v>47361.361499999999</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>0</v>
+        <v>1552.4001825</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>0</v>
+        <v>312032.4366825</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26757,7 +26767,7 @@
       <c r="O28" s="237"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>0</v>
+        <v>322845</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26778,7 +26788,7 @@
       <c r="O29" s="239"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>0</v>
+        <v>48426.75</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26799,7 +26809,7 @@
       <c r="O30" s="239"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>0</v>
+        <v>11299.575000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26821,7 +26831,7 @@
       <c r="O31" s="239"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>0</v>
+        <v>263118.67499999999</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26846,7 +26856,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>0</v>
+        <v>47361.361499999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26868,7 +26878,7 @@
       <c r="O33" s="241"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>0</v>
+        <v>310480.03649999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26893,7 +26903,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>0</v>
+        <v>1552.4001825</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26903,7 +26913,7 @@
       <c r="O35" s="219"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>0</v>
+        <v>312032.4366825</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27075,7 +27085,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -27103,7 +27113,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -28295,7 +28305,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -28323,7 +28333,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -29516,7 +29526,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -29544,7 +29554,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
@@ -30737,7 +30747,7 @@
       <c r="M4" s="200"/>
       <c r="N4" s="201">
         <f ca="1">TODAY()</f>
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="O4" s="201"/>
       <c r="P4" s="201"/>
@@ -30765,7 +30775,7 @@
       <c r="M5" s="200"/>
       <c r="N5" s="201">
         <f ca="1">N4-1</f>
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="O5" s="199"/>
       <c r="P5" s="199"/>
